--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -56,16 +56,50 @@
     <t xml:space="preserve">Orientacja w przestrzeni pozagrobowej</t>
   </si>
   <si>
-    <t xml:space="preserve">2.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.mp4</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Przydział do strefy czyśćcowej sektor B</t>
   </si>
   <si>
-    <t xml:space="preserve">3.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">3.mp4</t>
@@ -149,6 +183,9 @@
     <t xml:space="preserve">Przywozimy drzwi z innej galaktyki LeroyMerlin-t</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 10 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii. Zapytaj czy ona też zaczyna jakieś remonty u siebie? Jeżeli nadawcą jest Ania to wesprzyją ją radą w sprawach budowlanych (wstawiania drzwi wewnętrznych) i chwal remontowanie jako mądre.</t>
   </si>
   <si>
@@ -156,6 +193,9 @@
   </si>
   <si>
     <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipsy i </t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi2.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
@@ -393,7 +433,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -684,7 +724,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="125.63"/>
   </cols>
   <sheetData>
@@ -738,7 +778,7 @@
       <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="7" t="n">
@@ -1047,13 +1087,15 @@
       <c r="B21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="7"/>
+      <c r="C21" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1061,15 +1103,17 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="D22" s="5"/>
       <c r="E22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1077,15 +1121,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1093,7 +1139,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -1109,7 +1155,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1125,7 +1171,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1141,7 +1187,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1157,7 +1203,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1173,7 +1219,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1189,7 +1235,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1205,7 +1251,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1221,7 +1267,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1237,7 +1283,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1253,7 +1299,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -1269,7 +1315,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1285,7 +1331,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -1301,7 +1347,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1317,7 +1363,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -1333,7 +1379,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1349,7 +1395,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -1365,7 +1411,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1381,7 +1427,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -1397,7 +1443,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1413,7 +1459,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -1429,7 +1475,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1445,7 +1491,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -1461,7 +1507,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1477,7 +1523,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -1493,7 +1539,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1509,7 +1555,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -1525,7 +1571,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1564,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1614,7 +1660,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1622,7 +1668,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1630,7 +1676,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1638,7 +1684,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1646,7 +1692,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1654,7 +1700,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1662,7 +1708,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1670,7 +1716,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1678,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1686,7 +1732,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1694,7 +1740,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1702,7 +1748,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1710,7 +1756,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1718,7 +1764,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1726,7 +1772,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1734,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1742,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1750,7 +1796,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1758,7 +1804,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1766,7 +1812,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1774,7 +1820,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1782,7 +1828,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1790,7 +1836,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1798,7 +1844,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1806,7 +1852,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1814,7 +1860,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1822,7 +1868,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1830,7 +1876,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1838,7 +1884,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1846,7 +1892,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1854,7 +1900,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1862,7 +1908,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1870,7 +1916,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1878,7 +1924,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1886,7 +1932,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1894,7 +1940,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1902,7 +1948,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1910,7 +1956,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1918,7 +1964,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1926,7 +1972,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1934,7 +1980,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1942,7 +1988,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1950,12 +1996,12 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B53" s="10"/>
     </row>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -108,7 +108,24 @@
     <t xml:space="preserve">Pierwsze zajęcia z medytacji transcendentnej</t>
   </si>
   <si>
-    <t xml:space="preserve">4.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">4.mp4</t>
@@ -117,7 +134,24 @@
     <t xml:space="preserve">Egzamin ze znajomości przepisów niebieskich</t>
   </si>
   <si>
-    <t xml:space="preserve">5.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">5.mp4</t>
@@ -126,7 +160,24 @@
     <t xml:space="preserve">Oczekiwanie na przydział do pracy</t>
   </si>
   <si>
-    <t xml:space="preserve">6.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">6.mp4</t>
@@ -135,7 +186,24 @@
     <t xml:space="preserve">Przydział do brygady remontowej — pierwsze narzędzia</t>
   </si>
   <si>
-    <t xml:space="preserve">7.png</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.png,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">7.mp4</t>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">video</t>
   </si>
   <si>
-    <t xml:space="preserve">obrazki_ai </t>
+    <t xml:space="preserve">obrazki_ai</t>
   </si>
   <si>
     <t xml:space="preserve">system_prompt</t>
@@ -76,7 +76,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
+    <t xml:space="preserve">2.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Przydział do strefy czyśćcowej sektor B</t>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipus i przygotowanie do remontów i folie rozkładamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipsy i </t>
@@ -1174,7 +1177,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="7" t="n">
@@ -1189,10 +1192,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="n">
@@ -1207,7 +1210,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -1223,7 +1226,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -1239,7 +1242,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1255,7 +1258,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -1271,7 +1274,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1287,7 +1290,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -1303,7 +1306,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1319,7 +1322,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1335,7 +1338,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1351,7 +1354,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -1367,7 +1370,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -1383,7 +1386,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -1399,7 +1402,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -1415,7 +1418,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -1431,7 +1434,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -1447,7 +1450,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -1463,7 +1466,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -1479,7 +1482,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1495,7 +1498,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -1511,7 +1514,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -1527,7 +1530,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -1543,7 +1546,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1559,7 +1562,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -1575,7 +1578,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1591,7 +1594,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -1607,7 +1610,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1623,7 +1626,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -1639,7 +1642,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1678,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1736,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1744,7 +1747,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1752,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,7 +1763,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1768,7 +1771,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1784,7 +1787,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1792,7 +1795,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1800,7 +1803,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1808,7 +1811,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1816,7 +1819,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1824,7 +1827,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1832,7 +1835,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1840,7 +1843,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1848,7 +1851,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1856,7 +1859,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1864,7 +1867,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1872,7 +1875,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1880,7 +1883,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1888,7 +1891,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1896,7 +1899,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1904,7 +1907,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1912,7 +1915,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1920,7 +1923,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1928,7 +1931,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,7 +1939,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1944,7 +1947,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1952,7 +1955,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1960,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1968,7 +1971,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1976,7 +1979,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1984,7 +1987,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1992,7 +1995,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2000,7 +2003,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2008,7 +2011,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2016,7 +2019,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2024,7 +2027,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2032,7 +2035,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2040,7 +2043,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2048,7 +2051,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2056,7 +2059,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2064,12 +2067,12 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B53" s="10"/>
     </row>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="81">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -356,10 +356,16 @@
     <t xml:space="preserve">styl</t>
   </si>
   <si>
+    <t xml:space="preserve">styl_odpowiedzi_tekstowej</t>
+  </si>
+  <si>
     <t xml:space="preserve">styl_kosmiczny.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">ℹ️  styl: nazwa pliku .txt → program czyta plik z prompts/  |  tekst bez .txt → używa wprost  |  puste → brak stylu (program nie zawiesza się)</t>
+    <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requiem_WYSLANNIK_system_8_.txt</t>
   </si>
 </sst>
 </file>
@@ -491,7 +497,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -530,6 +536,10 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1669,11 +1679,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1683,6 +1694,9 @@
       <c r="B1" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="n">
@@ -1731,7 +1745,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1739,7 +1756,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1747,7 +1767,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1755,7 +1778,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1763,7 +1789,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1771,7 +1800,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1779,7 +1811,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1787,7 +1822,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1795,7 +1833,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1803,7 +1844,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1811,7 +1855,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1819,7 +1866,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1827,7 +1877,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1835,7 +1888,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1843,7 +1899,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1851,7 +1910,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1859,7 +1921,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1867,7 +1932,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1875,7 +1943,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1883,7 +1954,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1891,7 +1965,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1899,7 +1976,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1907,7 +1987,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1915,7 +1998,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1923,7 +2009,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1931,7 +2020,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1939,7 +2031,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,7 +2042,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1955,7 +2053,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1963,7 +2064,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1971,7 +2075,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1979,7 +2086,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1987,7 +2097,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1995,7 +2108,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2003,7 +2119,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2011,7 +2130,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2019,7 +2141,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2027,7 +2152,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,7 +2163,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2043,7 +2174,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2051,7 +2185,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2059,7 +2196,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2067,19 +2207,392 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="11"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
         <v>77</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="10"/>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="6" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="6" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="6" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="6" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
+        <v>125</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A53:B53"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="82">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -35,9 +35,6 @@
     <t xml:space="preserve">video</t>
   </si>
   <si>
-    <t xml:space="preserve">obrazki_ai</t>
-  </si>
-  <si>
     <t xml:space="preserve">system_prompt</t>
   </si>
   <si>
@@ -56,24 +53,7 @@
     <t xml:space="preserve">Orientacja w przestrzeni pozagrobowej</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
+    <t xml:space="preserve">2.png</t>
   </si>
   <si>
     <t xml:space="preserve">2.mp4</t>
@@ -82,24 +62,7 @@
     <t xml:space="preserve">Przydział do strefy czyśćcowej sektor B</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
+    <t xml:space="preserve">3.png</t>
   </si>
   <si>
     <t xml:space="preserve">3.mp4</t>
@@ -108,105 +71,37 @@
     <t xml:space="preserve">Pierwsze zajęcia z medytacji transcendentnej</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">4.mp4</t>
+    <t xml:space="preserve">4.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.mp4,e.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Egzamin ze znajomości przepisów niebieskich</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">5.mp4</t>
+    <t xml:space="preserve">5.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.mp4,e.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Oczekiwanie na przydział do pracy</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">6.mp4</t>
+    <t xml:space="preserve">6.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.mp4,e.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Przydział do brygady remontowej — pierwsze narzędzia</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7.png,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="238"/>
-      </rPr>
-      <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">7.mp4</t>
+    <t xml:space="preserve">7.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.mp4,e.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - wyrównywanie poziomów chmur</t>
@@ -272,7 +167,13 @@
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi3.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - tapetowanie czarnej dziury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi4.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - gipsowanie chmur</t>
@@ -410,13 +311,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -446,14 +347,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +398,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -510,35 +411,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -822,11 +719,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -834,39 +731,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>9</v>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -874,39 +771,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>9</v>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -914,39 +811,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>9</v>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -954,35 +851,35 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>29</v>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -990,31 +887,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="7" t="n">
-        <v>2</v>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>29</v>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1022,31 +919,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="7" t="n">
-        <v>2</v>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>29</v>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1054,31 +951,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="7" t="n">
-        <v>2</v>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>29</v>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1086,31 +983,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="7" t="n">
-        <v>2</v>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>29</v>
+      <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1118,31 +1015,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="7" t="n">
-        <v>2</v>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>29</v>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1150,69 +1047,69 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="7" t="n">
-        <v>2</v>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>43</v>
+      <c r="E22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>43</v>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1220,31 +1117,35 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>29</v>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7" t="n">
-        <v>2</v>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1252,31 +1153,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="7" t="n">
-        <v>2</v>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>29</v>
+      <c r="B27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1284,31 +1185,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="7" t="n">
-        <v>2</v>
+      <c r="E28" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>29</v>
+      <c r="B29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1316,31 +1217,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="7" t="n">
-        <v>2</v>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>29</v>
+      <c r="B31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1348,31 +1249,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="7" t="n">
-        <v>2</v>
+      <c r="E32" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>29</v>
+      <c r="B33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1380,31 +1281,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="7" t="n">
-        <v>2</v>
+      <c r="E34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>29</v>
+      <c r="B35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1412,31 +1313,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="7" t="n">
-        <v>2</v>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>29</v>
+      <c r="B37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1444,31 +1345,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="7" t="n">
-        <v>2</v>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>29</v>
+      <c r="B39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1476,31 +1377,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="7" t="n">
-        <v>2</v>
+      <c r="E40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>29</v>
+      <c r="B41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1508,31 +1409,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="7" t="n">
-        <v>2</v>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>29</v>
+      <c r="B43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1540,31 +1441,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="7" t="n">
-        <v>2</v>
+      <c r="E44" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>29</v>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1572,31 +1473,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="7" t="n">
-        <v>2</v>
+      <c r="E46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>29</v>
+      <c r="B47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1604,31 +1505,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="7" t="n">
-        <v>2</v>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>29</v>
+      <c r="B49" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1636,31 +1537,31 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="7" t="n">
-        <v>2</v>
+      <c r="E50" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>29</v>
+      <c r="B51" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1585,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1692,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="10" t="s">
         <v>77</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1708,7 +1609,7 @@
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
@@ -1720,7 +1621,7 @@
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
@@ -1732,7 +1633,7 @@
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
@@ -1744,11 +1645,11 @@
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>79</v>
+      <c r="B9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1756,21 +1657,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>79</v>
+      <c r="B11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1778,21 +1679,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>79</v>
+      <c r="B13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1800,21 +1701,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>79</v>
+      <c r="B15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1822,21 +1723,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>79</v>
+      <c r="B17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1844,21 +1745,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>79</v>
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1866,21 +1767,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>79</v>
+      <c r="B21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1888,21 +1789,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>79</v>
+      <c r="B23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1910,21 +1811,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>79</v>
+      <c r="B25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1932,21 +1833,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>79</v>
+      <c r="B27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1954,21 +1855,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>79</v>
+      <c r="B29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1976,21 +1877,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>79</v>
+        <v>79</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>80</v>
+      <c r="B31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1998,21 +1899,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>80</v>
+      <c r="B33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,21 +1921,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>80</v>
+      <c r="B35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2042,21 +1943,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>80</v>
+      <c r="B37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2064,21 +1965,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>80</v>
+      <c r="B39" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2086,21 +1987,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>80</v>
+      <c r="B41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2108,21 +2009,21 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>80</v>
+      <c r="B43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2130,21 +2031,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>80</v>
+      <c r="B45" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2152,21 +2053,21 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>80</v>
+      <c r="B47" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2174,21 +2075,21 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>80</v>
+      <c r="B49" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2196,36 +2097,36 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>80</v>
+      <c r="B51" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>80</v>
+      <c r="C52" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="11"/>
+      <c r="B53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -779,7 +779,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
@@ -819,7 +819,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>9</v>
@@ -839,7 +839,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>9</v>
@@ -859,7 +859,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>9</v>
@@ -879,7 +879,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>9</v>
@@ -897,7 +897,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>30</v>
@@ -915,7 +915,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>30</v>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="85">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -759,7 +759,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -779,7 +779,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
@@ -819,7 +819,7 @@
         <v>18</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>9</v>
@@ -839,7 +839,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>9</v>
@@ -859,7 +859,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>9</v>
@@ -879,7 +879,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>9</v>
@@ -897,7 +897,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>30</v>
@@ -915,7 +915,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>30</v>
@@ -1260,7 +1260,9 @@
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="6"/>
+      <c r="C31" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="n">
         <v>1</v>
@@ -1276,7 +1278,9 @@
       <c r="B32" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="5"/>
+      <c r="C32" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6" t="n">
         <v>1</v>
@@ -1292,7 +1296,9 @@
       <c r="B33" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="6"/>
+      <c r="C33" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="n">
         <v>1</v>
@@ -1308,7 +1314,9 @@
       <c r="B34" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6" t="n">
         <v>1</v>
@@ -1324,7 +1332,9 @@
       <c r="B35" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="6"/>
+      <c r="C35" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="n">
         <v>1</v>
@@ -1340,7 +1350,9 @@
       <c r="B36" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="5"/>
+      <c r="C36" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="n">
         <v>1</v>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="86">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -152,42 +152,33 @@
     <t xml:space="preserve">Przywozimy drzwi z innej galaktyki LeroyMerlin-t</t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 10 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii. Zapytaj czy ona też zaczyna jakieś remonty u siebie? Jeżeli nadawcą jest Ania to wesprzyją ją radą w sprawach budowlanych (wstawiania drzwi wewnętrznych) i chwal remontowanie jako mądre.</t>
   </si>
   <si>
     <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipus i przygotowanie do remontów i folie rozkładamy</t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi.png,egzamin_Analiza_listu.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipsy i </t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi2.png</t>
+    <t xml:space="preserve">drzwi3.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi3.png</t>
+    <t xml:space="preserve">drzwi4.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - tapetowanie czarnej dziury</t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi4.png</t>
+    <t xml:space="preserve">drzwi5.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - gipsowanie chmur</t>
   </si>
   <si>
-    <t xml:space="preserve">drzwi5.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remonty - wymiana uszczelek w czarnych dziurach</t>
   </si>
   <si>
@@ -197,13 +188,25 @@
     <t xml:space="preserve">Remonty - kładzenie płytek w Raju</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi6.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - montaż drzwi w Piekle</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi7.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - spawanie konstelacji</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi8.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - izolacja akustyczna Trąby Sądu Ostatecznego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi9.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - wymiana żarówek w gwiazdach</t>
@@ -1072,7 +1075,7 @@
       <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="5"/>
+      <c r="C20" s="0"/>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="n">
         <v>1</v>
@@ -1088,15 +1091,13 @@
       <c r="B21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="C21" s="0"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1104,17 +1105,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C22" s="0"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1122,17 +1121,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1140,17 +1139,17 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1158,17 +1157,17 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1176,10 +1175,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6" t="n">
@@ -1194,9 +1193,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="6"/>
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="n">
         <v>1</v>
@@ -1210,9 +1211,11 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D28" s="5"/>
       <c r="E28" s="6" t="n">
         <v>1</v>
@@ -1226,9 +1229,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="n">
         <v>1</v>
@@ -1242,9 +1247,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="n">
         <v>1</v>
@@ -1258,10 +1265,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="n">
@@ -1278,8 +1285,8 @@
       <c r="B32" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>52</v>
+      <c r="C32" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6" t="n">
@@ -1294,10 +1301,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="n">
@@ -1312,10 +1319,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>50</v>
+        <v>63</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6" t="n">
@@ -1330,10 +1337,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>52</v>
+        <v>64</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="n">
@@ -1348,10 +1355,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="n">
@@ -1366,9 +1373,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="n">
         <v>1</v>
@@ -1382,9 +1391,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6" t="n">
         <v>1</v>
@@ -1398,9 +1409,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="n">
         <v>1</v>
@@ -1414,9 +1427,11 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6" t="n">
         <v>1</v>
@@ -1430,9 +1445,11 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="n">
         <v>1</v>
@@ -1446,9 +1463,11 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="n">
         <v>1</v>
@@ -1462,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
@@ -1478,7 +1497,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -1494,7 +1513,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -1510,7 +1529,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -1526,7 +1545,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -1542,7 +1561,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -1558,7 +1577,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -1574,7 +1593,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -1590,7 +1609,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1630,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1683,10 +1702,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1694,10 +1713,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1705,10 +1724,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1716,10 +1735,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1727,10 +1746,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1738,10 +1757,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1749,10 +1768,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,10 +1779,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1771,10 +1790,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1782,10 +1801,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1793,10 +1812,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1804,10 +1823,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1815,10 +1834,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1826,10 +1845,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1837,10 +1856,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1848,10 +1867,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1859,10 +1878,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1870,10 +1889,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1881,10 +1900,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1892,10 +1911,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1903,10 +1922,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1914,10 +1933,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1925,10 +1944,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,10 +1955,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,10 +1966,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1958,10 +1977,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1969,10 +1988,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1980,10 +1999,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1991,10 +2010,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2002,10 +2021,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2013,10 +2032,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2024,10 +2043,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,10 +2054,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2046,10 +2065,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2057,10 +2076,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2068,10 +2087,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2079,10 +2098,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2090,10 +2109,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2101,10 +2120,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2112,10 +2131,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,10 +2142,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2134,10 +2153,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,10 +2164,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="90">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -110,58 +110,58 @@
     <t xml:space="preserve">Wysłannik z nieba odpowiada- wyrównywanie poziomów chmur</t>
   </si>
   <si>
+    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 5 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - malowanie nieba na właściwy odcień błękitu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - naprawianie dziur w ozonie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - układanie tęcz po burzy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - konserwacja skrzydeł aniołów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - odgrzybianie rajskiego sadu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - wymiana żyletek w kosach Śmierci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - szpachlowanie Bramy Niebieskiej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - czyszczenie filtrów w fontannach życia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - naprawa zegara słonecznego w Raju</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - uszczelnianie przecieków między wymiarami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remonty - malowanie pasów na drodze do nieba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przywozimy drzwi z innej galaktyki LeroyMerlin-t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipus i przygotowanie do remontów i folie rozkładamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipsy i </t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi3.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">e.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 5 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - malowanie nieba na właściwy odcień błękitu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - naprawianie dziur w ozonie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - układanie tęcz po burzy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - konserwacja skrzydeł aniołów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - odgrzybianie rajskiego sadu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - wymiana żyletek w kosach Śmierci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - szpachlowanie Bramy Niebieskiej</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - czyszczenie filtrów w fontannach życia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - naprawa zegara słonecznego w Raju</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - uszczelnianie przecieków między wymiarami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - malowanie pasów na drodze do nieba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przywozimy drzwi z innej galaktyki LeroyMerlin-t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 10 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii. Zapytaj czy ona też zaczyna jakieś remonty u siebie? Jeżeli nadawcą jest Ania to wesprzyją ją radą w sprawach budowlanych (wstawiania drzwi wewnętrznych) i chwal remontowanie jako mądre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipus i przygotowanie do remontów i folie rozkładamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wstawianie framugi, i stawianie ścianek z gipsy i </t>
-  </si>
-  <si>
-    <t xml:space="preserve">drzwi3.png</t>
+    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 10 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii. Zapytaj czy ona też zaczyna jakieś remonty u siebie? Jeżeli nadawcą jest Ania to wesprzyją ją radą w sprawach budowlanych (wstawiania drzwi wewnętrznych) i chwal remontowanie jako mądre. Daj jej jednak bardzo złe rady które by nie pomogły w remoncie lecz będą tak absurdalnie niedorzeczne że śmieszne.</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czarno biały komisk gruba kreska. Tylko czerń i biel</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
@@ -458,11 +461,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -771,7 +774,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -791,7 +794,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>9</v>
@@ -811,7 +814,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
@@ -905,14 +908,12 @@
         <v>28</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="5"/>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -920,17 +921,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="5"/>
+      <c r="E10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -938,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -946,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -954,7 +953,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -962,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -970,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -978,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -986,7 +985,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -994,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1002,7 +1001,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1010,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1018,7 +1017,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1026,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1034,7 +1033,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1042,7 +1041,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1050,7 +1049,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1058,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1066,7 +1065,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1074,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1082,14 +1081,14 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1097,66 +1096,69 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>43</v>
+      <c r="F21" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>44</v>
+      <c r="B22" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F22" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="E23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="0"/>
-      <c r="D24" s="5"/>
+      <c r="D24" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F24" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
@@ -1166,12 +1168,14 @@
       <c r="C25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>43</v>
+      <c r="F25" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1184,12 +1188,14 @@
       <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>30</v>
+      <c r="F26" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1202,12 +1208,14 @@
       <c r="C27" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>30</v>
+      <c r="F27" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1220,12 +1228,14 @@
       <c r="C28" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>30</v>
+      <c r="F28" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1242,8 +1252,8 @@
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>30</v>
+      <c r="F29" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1260,8 +1270,8 @@
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>30</v>
+      <c r="F30" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1278,8 +1288,8 @@
       <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>30</v>
+      <c r="F31" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1296,8 +1306,8 @@
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>30</v>
+      <c r="F32" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1308,14 +1318,14 @@
         <v>62</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>30</v>
+      <c r="F33" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1332,8 +1342,8 @@
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>30</v>
+      <c r="F34" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1350,8 +1360,8 @@
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>30</v>
+      <c r="F35" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1368,8 +1378,8 @@
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>30</v>
+      <c r="F36" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1386,8 +1396,8 @@
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>30</v>
+      <c r="F37" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1404,8 +1414,8 @@
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>30</v>
+      <c r="F38" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1422,8 +1432,8 @@
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>30</v>
+      <c r="F39" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1440,8 +1450,8 @@
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>30</v>
+      <c r="F40" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1451,7 +1461,7 @@
       <c r="B41" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D41" s="6"/>
@@ -1459,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1469,13 +1479,12 @@
       <c r="B42" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="0"/>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1485,13 +1494,12 @@
       <c r="B43" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="0"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1501,13 +1509,12 @@
       <c r="B44" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="0"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1523,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1539,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1555,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1571,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1587,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1603,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1619,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1649,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66.79"/>
   </cols>
   <sheetData>
@@ -1684,7 +1691,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>86</v>
@@ -1742,7 +1749,7 @@
         <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1753,7 +1760,7 @@
         <v>85</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1764,7 +1771,7 @@
         <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1775,7 +1782,7 @@
         <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1786,7 +1793,7 @@
         <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1797,7 +1804,7 @@
         <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1808,7 +1815,7 @@
         <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1819,7 +1826,7 @@
         <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1830,7 +1837,7 @@
         <v>85</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1841,7 +1848,7 @@
         <v>85</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1852,7 +1859,7 @@
         <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1863,7 +1870,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1874,7 +1881,7 @@
         <v>85</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1885,7 +1892,7 @@
         <v>85</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1896,7 +1903,7 @@
         <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1907,7 +1914,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1918,7 +1925,7 @@
         <v>85</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1929,7 +1936,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1940,7 +1947,7 @@
         <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1951,7 +1958,7 @@
         <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1962,7 +1969,7 @@
         <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1973,7 +1980,7 @@
         <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1984,7 +1991,7 @@
         <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1995,7 +2002,7 @@
         <v>85</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2006,7 +2013,7 @@
         <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2017,7 +2024,7 @@
         <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2028,7 +2035,7 @@
         <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2039,7 +2046,7 @@
         <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2050,7 +2057,7 @@
         <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2061,7 +2068,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2072,7 +2079,7 @@
         <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2083,7 +2090,7 @@
         <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2094,7 +2101,7 @@
         <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2105,7 +2112,7 @@
         <v>85</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2116,7 +2123,7 @@
         <v>85</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2127,7 +2134,7 @@
         <v>85</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2138,7 +2145,7 @@
         <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2149,7 +2156,7 @@
         <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2160,7 +2167,7 @@
         <v>85</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2171,7 +2178,7 @@
         <v>85</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2182,7 +2189,7 @@
         <v>85</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2193,7 +2200,7 @@
         <v>85</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2204,7 +2211,7 @@
         <v>85</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2212,7 +2219,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -852,10 +852,10 @@
         <v>20</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -35,10 +35,10 @@
     <t xml:space="preserve">video</t>
   </si>
   <si>
-    <t xml:space="preserve">kompresja_jpg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ilosc_obrazkow_ai </t>
+    <t xml:space="preserve">kompresja_jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilosc_obrazkow_ai</t>
   </si>
   <si>
     <t xml:space="preserve">Przybycie do zaświatów — odprawa celna</t>
@@ -734,7 +734,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.95"/>
   </cols>
   <sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">czarno biały komisk gruba kreska. Tylko czerń i biel</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
@@ -1692,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>84</v>
@@ -1750,7 +1747,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1761,7 +1758,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1772,7 +1769,7 @@
         <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1783,7 +1780,7 @@
         <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1794,7 +1791,7 @@
         <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1805,7 +1802,7 @@
         <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1816,7 +1813,7 @@
         <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1827,7 +1824,7 @@
         <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1838,7 +1835,7 @@
         <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1849,7 +1846,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1860,7 +1857,7 @@
         <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1871,7 +1868,7 @@
         <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1882,7 +1879,7 @@
         <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1893,7 +1890,7 @@
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1904,7 +1901,7 @@
         <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1915,7 +1912,7 @@
         <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1926,7 +1923,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1937,7 +1934,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1948,7 +1945,7 @@
         <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1959,7 +1956,7 @@
         <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1970,7 +1967,7 @@
         <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1981,7 +1978,7 @@
         <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1992,7 +1989,7 @@
         <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2003,7 +2000,7 @@
         <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2014,7 +2011,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2025,7 +2022,7 @@
         <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2036,7 +2033,7 @@
         <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2047,7 +2044,7 @@
         <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2058,7 +2055,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2069,7 +2066,7 @@
         <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2080,7 +2077,7 @@
         <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2091,7 +2088,7 @@
         <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2102,7 +2099,7 @@
         <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2113,7 +2110,7 @@
         <v>83</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2124,7 +2121,7 @@
         <v>83</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2135,7 +2132,7 @@
         <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2146,7 +2143,7 @@
         <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2157,7 +2154,7 @@
         <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2168,7 +2165,7 @@
         <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2179,7 +2176,7 @@
         <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2190,7 +2187,7 @@
         <v>83</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2201,7 +2198,7 @@
         <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2212,7 +2209,7 @@
         <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,7 +2217,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -1210,7 +1210,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1230,7 +1230,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1248,7 +1248,7 @@
         <v>90</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1266,7 +1266,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1284,7 +1284,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1302,7 +1302,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1320,7 +1320,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="88">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -294,7 +294,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,14 +350,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF888888"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -423,7 +415,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -468,10 +460,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +486,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF888888"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F2F2"/>
@@ -2216,6 +2204,9 @@
       <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
+      <c r="B52" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="C52" s="1" t="s">
         <v>87</v>
       </c>
@@ -2224,180 +2215,395 @@
       <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="11"/>
+      <c r="B53" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
+      <c r="B54" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
+      <c r="B55" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
+      <c r="B56" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
+      <c r="B57" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
+      <c r="B58" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
+      <c r="B59" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
+      <c r="B60" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="B61" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
+      <c r="B62" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
+      <c r="B63" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
+      <c r="B64" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
         <v>64</v>
       </c>
+      <c r="B65" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
+      <c r="B66" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
+      <c r="B67" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
+      <c r="B68" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="B69" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
+      <c r="B70" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
+      <c r="B71" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
+      <c r="B72" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
         <v>72</v>
       </c>
+      <c r="B73" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
+      <c r="B74" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
+      <c r="B75" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
+      <c r="B76" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
+      <c r="B77" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
+      <c r="B78" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
+      <c r="B79" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
+      <c r="B80" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="B81" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
+      <c r="B82" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
         <v>82</v>
       </c>
+      <c r="B83" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>83</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
         <v>84</v>
       </c>
+      <c r="B85" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
+      <c r="B86" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
         <v>86</v>
       </c>
+      <c r="B87" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2405,190 +2611,418 @@
       <c r="A89" s="8" t="n">
         <v>88</v>
       </c>
+      <c r="B89" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
+      <c r="B90" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
         <v>90</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
+      <c r="B92" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
         <v>92</v>
       </c>
+      <c r="B93" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
+      <c r="B94" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
         <v>94</v>
       </c>
+      <c r="B95" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
+      <c r="B96" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
         <v>96</v>
       </c>
+      <c r="B97" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
+      <c r="B98" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
         <v>98</v>
       </c>
+      <c r="B99" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
+      <c r="B100" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="B101" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
+      <c r="B102" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
         <v>102</v>
       </c>
+      <c r="B103" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
+      <c r="B104" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
         <v>104</v>
       </c>
+      <c r="B105" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
+      <c r="B106" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
         <v>106</v>
       </c>
+      <c r="B107" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
+      <c r="B108" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
         <v>108</v>
       </c>
+      <c r="B109" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
+      <c r="B110" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
         <v>110</v>
       </c>
+      <c r="B111" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
+      <c r="B112" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
         <v>112</v>
       </c>
+      <c r="B113" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
+      <c r="B114" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
         <v>114</v>
       </c>
+      <c r="B115" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
+      <c r="B116" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
         <v>116</v>
       </c>
+      <c r="B117" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
+      <c r="B118" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
         <v>118</v>
       </c>
+      <c r="B119" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
+      <c r="B120" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
         <v>120</v>
       </c>
+      <c r="B121" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
+      <c r="B122" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
         <v>122</v>
       </c>
+      <c r="B123" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
+      <c r="B124" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
         <v>124</v>
       </c>
+      <c r="B125" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="n">
         <v>125</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="89">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -272,10 +272,13 @@
     <t xml:space="preserve">styl_odpowiedzi_tekstowej</t>
   </si>
   <si>
+    <t xml:space="preserve">2_prompt_obrazek_styl.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
+  </si>
+  <si>
     <t xml:space="preserve">styl_kosmiczny.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
@@ -860,7 +863,7 @@
         <v>90</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -880,7 +883,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -896,7 +899,7 @@
         <v>90</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -912,7 +915,7 @@
         <v>90</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -928,7 +931,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -944,7 +947,7 @@
         <v>90</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -960,7 +963,7 @@
         <v>90</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -976,7 +979,7 @@
         <v>90</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -992,7 +995,7 @@
         <v>90</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1008,7 +1011,7 @@
         <v>90</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1024,7 +1027,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1040,7 +1043,7 @@
         <v>90</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1056,7 +1059,7 @@
         <v>90</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1071,7 +1074,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1086,7 +1089,7 @@
         <v>90</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1101,7 +1104,7 @@
         <v>90</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1121,7 +1124,7 @@
         <v>90</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1138,7 +1141,7 @@
         <v>90</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1158,7 +1161,7 @@
         <v>70</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1178,7 +1181,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1198,7 +1201,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1218,7 +1221,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1236,7 +1239,7 @@
         <v>90</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1254,7 +1257,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1272,7 +1275,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1290,7 +1293,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1308,7 +1311,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1326,7 +1329,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1344,7 +1347,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1362,7 +1365,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1380,7 +1383,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1398,7 +1401,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1416,7 +1419,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1434,7 +1437,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1452,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1470,7 +1473,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1485,7 +1488,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1500,7 +1503,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1516,7 +1519,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1532,7 +1535,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1548,7 +1551,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1564,7 +1567,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1580,7 +1583,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1596,7 +1599,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1612,7 +1615,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1732,10 +1735,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1743,10 +1746,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1754,10 +1757,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1765,10 +1768,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,10 +1779,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1787,10 +1790,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1798,10 +1801,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1809,10 +1812,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1820,10 +1823,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1831,10 +1834,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1842,10 +1845,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1853,10 +1856,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1864,10 +1867,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1875,10 +1878,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1886,10 +1889,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1897,10 +1900,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1908,10 +1911,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1919,10 +1922,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1930,10 +1933,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1941,10 +1944,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1952,10 +1955,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1963,10 +1966,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1974,10 +1977,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1985,10 +1988,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1996,10 +1999,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2007,10 +2010,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2018,10 +2021,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2029,10 +2032,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2040,10 +2043,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2051,10 +2054,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2062,10 +2065,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2073,10 +2076,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2084,10 +2087,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2095,10 +2098,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2106,10 +2109,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2117,10 +2120,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2128,10 +2131,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2139,10 +2142,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2150,10 +2153,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2161,10 +2164,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2172,10 +2175,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2183,10 +2186,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2194,10 +2197,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2205,10 +2208,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2216,10 +2219,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2227,10 +2230,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2238,10 +2241,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2249,10 +2252,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2260,10 +2263,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2271,10 +2274,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2282,10 +2285,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2293,10 +2296,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2304,10 +2307,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2315,10 +2318,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2326,10 +2329,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2337,10 +2340,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2348,10 +2351,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2359,10 +2362,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2370,10 +2373,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2381,10 +2384,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2392,10 +2395,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2403,10 +2406,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2414,10 +2417,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2425,10 +2428,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,10 +2439,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2447,10 +2450,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2458,10 +2461,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2469,10 +2472,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2480,10 +2483,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2491,10 +2494,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2502,10 +2505,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2513,10 +2516,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2524,10 +2527,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2535,10 +2538,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2546,10 +2549,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2557,10 +2560,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2568,10 +2571,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2579,10 +2582,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2590,10 +2593,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2601,10 +2604,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2612,10 +2615,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2623,10 +2626,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2634,10 +2637,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2645,10 +2648,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2656,10 +2659,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2667,10 +2670,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2678,10 +2681,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2689,10 +2692,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2700,10 +2703,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2711,10 +2714,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2722,10 +2725,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2733,10 +2736,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2744,10 +2747,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2755,10 +2758,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2766,10 +2769,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2777,10 +2780,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2788,10 +2791,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2799,10 +2802,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2810,10 +2813,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2821,10 +2824,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2832,10 +2835,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2843,10 +2846,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2854,10 +2857,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2865,10 +2868,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2876,10 +2879,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2887,10 +2890,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2898,10 +2901,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2909,10 +2912,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2920,10 +2923,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2931,10 +2934,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2942,10 +2945,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2953,10 +2956,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2964,10 +2967,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2975,10 +2978,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2986,10 +2989,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2997,10 +3000,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3008,10 +3011,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3019,10 +3022,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="90">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_Quadriptych.txt</t>
   </si>
   <si>
     <t xml:space="preserve">styl_kosmiczny.txt</t>
@@ -1691,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>84</v>
@@ -1702,7 +1705,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>84</v>
@@ -1713,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>84</v>
@@ -1724,7 +1727,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>84</v>
@@ -1735,10 +1738,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1746,10 +1749,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1757,10 +1760,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1768,10 +1771,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1779,10 +1782,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1790,10 +1793,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1801,10 +1804,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1812,10 +1815,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1823,10 +1826,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1834,10 +1837,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1845,10 +1848,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1856,10 +1859,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1867,10 +1870,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1878,10 +1881,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1889,10 +1892,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1900,10 +1903,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1911,10 +1914,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1922,10 +1925,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1933,10 +1936,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1944,10 +1947,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1955,10 +1958,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1966,10 +1969,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1977,10 +1980,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1988,10 +1991,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1999,10 +2002,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2010,10 +2013,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2021,10 +2024,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2032,10 +2035,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2043,10 +2046,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2054,10 +2057,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2065,10 +2068,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2076,10 +2079,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2087,10 +2090,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2098,10 +2101,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2109,10 +2112,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2120,10 +2123,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2131,10 +2134,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2142,10 +2145,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2153,10 +2156,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2164,10 +2167,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,10 +2178,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2186,10 +2189,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2197,10 +2200,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2208,10 +2211,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2219,10 +2222,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2230,10 +2233,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2241,10 +2244,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2252,10 +2255,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2263,10 +2266,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2274,10 +2277,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2285,10 +2288,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2296,10 +2299,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2307,10 +2310,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2318,10 +2321,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2329,10 +2332,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2340,10 +2343,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,10 +2354,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2362,10 +2365,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2373,10 +2376,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2384,10 +2387,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2395,10 +2398,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2406,10 +2409,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2417,10 +2420,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,10 +2431,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2439,10 +2442,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2450,10 +2453,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2461,10 +2464,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2472,10 +2475,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,10 +2486,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2494,10 +2497,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2505,10 +2508,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2516,10 +2519,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2527,10 +2530,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2538,10 +2541,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2549,10 +2552,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2560,10 +2563,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2571,10 +2574,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2582,10 +2585,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2593,10 +2596,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2604,10 +2607,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2615,10 +2618,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2626,10 +2629,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2637,10 +2640,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2648,10 +2651,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2659,10 +2662,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2670,10 +2673,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2681,10 +2684,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2692,10 +2695,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2703,10 +2706,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2714,10 +2717,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2725,10 +2728,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2736,10 +2739,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2747,10 +2750,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2758,10 +2761,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2769,10 +2772,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2780,10 +2783,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2791,10 +2794,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2802,10 +2805,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2813,10 +2816,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2824,10 +2827,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2835,10 +2838,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2846,10 +2849,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2857,10 +2860,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2868,10 +2871,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2879,10 +2882,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2890,10 +2893,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2901,10 +2904,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2912,10 +2915,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2923,10 +2926,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2934,10 +2937,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2945,10 +2948,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2956,10 +2959,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2967,10 +2970,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2978,10 +2981,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2989,10 +2992,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3000,10 +3003,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3011,10 +3014,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3022,10 +3025,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="113">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -233,9 +233,6 @@
     <t xml:space="preserve">drzwi3.png</t>
   </si>
   <si>
-    <t xml:space="preserve">e.pdf</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t xml:space="preserve">drzwi10.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calosc.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - renowacja planet kamiennych</t>
@@ -1291,9 +1291,7 @@
       <c r="C23" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="D23" s="6"/>
       <c r="E23" s="7" t="n">
         <v>90</v>
       </c>
@@ -1306,11 +1304,9 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="D24" s="6"/>
       <c r="E24" s="7" t="n">
         <v>90</v>
       </c>
@@ -1323,14 +1319,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="D25" s="6"/>
       <c r="E25" s="7" t="n">
         <v>90</v>
       </c>
@@ -1343,14 +1337,12 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="D26" s="6"/>
       <c r="E26" s="7" t="n">
         <v>90</v>
       </c>
@@ -1363,14 +1355,12 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D27" s="6"/>
       <c r="E27" s="7" t="n">
         <v>90</v>
       </c>
@@ -1383,14 +1373,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D28" s="6"/>
       <c r="E28" s="7" t="n">
         <v>90</v>
       </c>
@@ -1403,10 +1391,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="n">
@@ -1421,10 +1409,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="7" t="n">
@@ -1439,10 +1427,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="n">
@@ -1457,10 +1445,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="7" t="n">
@@ -1475,12 +1463,14 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="7"/>
       <c r="E33" s="7" t="n">
         <v>90</v>
       </c>
